--- a/data/trans_dic/DC_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/DC_R-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,5; 22,47</t>
+          <t>15,47; 22,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,25; 38,99</t>
+          <t>31,09; 38,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,6; 29,03</t>
+          <t>23,42; 28,89</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,06; 23,61</t>
+          <t>16,32; 23,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,85; 41,85</t>
+          <t>33,44; 41,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,8; 30,64</t>
+          <t>24,78; 30,55</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 29,12</t>
+          <t>7,02; 28,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41,69; 53,8</t>
+          <t>41,51; 53,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,36; 34,19</t>
+          <t>11,01; 33,74</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,15; 29,52</t>
+          <t>24,17; 29,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,51; 74,24</t>
+          <t>36,54; 70,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,8; 55,76</t>
+          <t>30,67; 58,32</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,69; 31,0</t>
+          <t>22,82; 31,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,13; 64,07</t>
+          <t>45,22; 63,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37,71; 52,25</t>
+          <t>37,83; 51,95</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,96; 19,12</t>
+          <t>5,55; 19,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35,5; 41,67</t>
+          <t>35,52; 41,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,04; 34,82</t>
+          <t>29,03; 35,23</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,1; 23,73</t>
+          <t>17,05; 23,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40,49; 56,78</t>
+          <t>40,2; 54,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30,05; 40,63</t>
+          <t>30,07; 39,95</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>78319; 113498</t>
+          <t>78170; 111641</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>139812; 174470</t>
+          <t>139104; 172645</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>224789; 276533</t>
+          <t>223136; 275231</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72613; 106768</t>
+          <t>73812; 105061</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>125674; 160105</t>
+          <t>127937; 159373</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>207055; 255798</t>
+          <t>206899; 255040</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39225; 194609</t>
+          <t>46928; 193563</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>69589; 89791</t>
+          <t>69279; 89123</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86560; 285511</t>
+          <t>91924; 281808</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>249895; 305476</t>
+          <t>250091; 309099</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>357135; 726178</t>
+          <t>357372; 691471</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>620010; 1122357</t>
+          <t>617297; 1173967</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>107793; 147267</t>
+          <t>108411; 147254</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>379674; 539066</t>
+          <t>380424; 534236</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>496407; 687841</t>
+          <t>497986; 683908</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14339; 45985</t>
+          <t>13337; 45843</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>270315; 317286</t>
+          <t>270428; 316979</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>290975; 348812</t>
+          <t>290832; 352952</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>577273; 801170</t>
+          <t>575667; 801587</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1448714; 2031324</t>
+          <t>1438371; 1940187</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2089952; 2825273</t>
+          <t>2091030; 2778251</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DC_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/DC_R-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,47; 22,1</t>
+          <t>15,68; 22,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,09; 38,58</t>
+          <t>31,52; 39,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,42; 28,89</t>
+          <t>24,15; 29,07</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,32; 23,23</t>
+          <t>15,87; 22,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,44; 41,66</t>
+          <t>34,37; 42,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,78; 30,55</t>
+          <t>25,52; 31,34</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,02; 28,96</t>
+          <t>23,04; 31,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41,51; 53,4</t>
+          <t>42,01; 53,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,01; 33,74</t>
+          <t>29,74; 36,51</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,17; 29,87</t>
+          <t>23,38; 28,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,54; 70,7</t>
+          <t>35,46; 41,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,67; 58,32</t>
+          <t>29,32; 33,14</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,82; 31,0</t>
+          <t>21,7; 29,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,22; 63,5</t>
+          <t>45,27; 50,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37,83; 51,95</t>
+          <t>36,58; 41,45</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,55; 19,06</t>
+          <t>6,34; 18,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35,52; 41,63</t>
+          <t>35,25; 41,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,03; 35,23</t>
+          <t>29,23; 35,17</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,05; 23,74</t>
+          <t>21,41; 24,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40,2; 54,23</t>
+          <t>39,07; 41,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30,07; 39,95</t>
+          <t>30,89; 32,95</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>93889</t>
+          <t>103099</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>156423</t>
+          <t>171920</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250312</t>
+          <t>275019</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>78170; 111641</t>
+          <t>86336; 121954</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>139104; 172645</t>
+          <t>153952; 192007</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>223136; 275231</t>
+          <t>250907; 302018</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>88800</t>
+          <t>93409</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>142406</t>
+          <t>161647</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>231206</t>
+          <t>255056</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73812; 105061</t>
+          <t>76698; 109810</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>127937; 159373</t>
+          <t>145430; 180251</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>206899; 255040</t>
+          <t>231276; 284090</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>116923</t>
+          <t>128428</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79769</t>
+          <t>89955</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>196691</t>
+          <t>218384</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>46928; 193563</t>
+          <t>108637; 148242</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>69279; 89123</t>
+          <t>78774; 100707</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91924; 281808</t>
+          <t>196030; 240660</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>275632</t>
+          <t>293722</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>496495</t>
+          <t>328944</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>772126</t>
+          <t>622665</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>250091; 309099</t>
+          <t>264642; 327202</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>357372; 691471</t>
+          <t>305373; 354362</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>617297; 1173967</t>
+          <t>584373; 660447</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>126343</t>
+          <t>143331</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>431613</t>
+          <t>399564</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>557956</t>
+          <t>542895</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>108411; 147254</t>
+          <t>123266; 166611</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>380424; 534236</t>
+          <t>376154; 423185</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>497986; 683908</t>
+          <t>511708; 579815</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>25989</t>
+          <t>25693</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>294322</t>
+          <t>322428</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>320311</t>
+          <t>348121</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13337; 45843</t>
+          <t>15034; 43298</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>270428; 316979</t>
+          <t>297624; 350627</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>290832; 352952</t>
+          <t>316089; 380327</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>727576</t>
+          <t>787682</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1601027</t>
+          <t>1474457</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2328603</t>
+          <t>2262139</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>575667; 801587</t>
+          <t>737161; 843371</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1438371; 1940187</t>
+          <t>1420303; 1523550</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2091030; 2778251</t>
+          <t>2186176; 2332468</t>
         </is>
       </c>
     </row>
